--- a/etf_holdings/2026-09-14_00990A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-14_00990A_full_holdings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-14 19:16:57</t>
+          <t>2026-09-14 23:57:53</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -504,40 +504,40 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2454聯發科</t>
+          <t>2383台光電</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-0.55%4560</t>
+          <t>-0.37%5345</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-0.55%</t>
+          <t>-0.37%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>4560</t>
+          <t>5345</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3.19%243,000</t>
+          <t>3.16%212,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>3.19%</t>
+          <t>3.16%</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>243000</v>
+        <v>212000</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-14 19:16:57</t>
+          <t>2026-09-14 23:57:53</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -567,40 +567,40 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2383台光電</t>
+          <t>2454聯發科</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-0.37%5345</t>
+          <t>-0.55%4560</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-0.37%</t>
+          <t>-0.55%</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>5345</t>
+          <t>4560</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3.16%212,000</t>
+          <t>3.10%243,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>3.16%</t>
+          <t>3.10%</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>212000</v>
+        <v>243000</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-14 19:16:57</t>
+          <t>2026-09-14 23:57:53</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,12 +650,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2.76%406,000</t>
+          <t>2.72%406,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2.76%</t>
+          <t>2.72%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-14 19:16:58</t>
+          <t>2026-09-14 23:57:54</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -693,40 +693,40 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2308台達電</t>
+          <t>6981MURATA MANUFACTURING CO LTD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0%1620</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1620</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2.05%441,000</t>
+          <t>2.00%477,100</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2.05%</t>
+          <t>2.00%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>441000</v>
+        <v>477100</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-14 19:16:58</t>
+          <t>2026-09-14 23:57:54</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -756,40 +756,40 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>6981MURATA MANUFACTURING CO LTD</t>
+          <t>2308台達電</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>0%1620</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1620</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2.05%477,100</t>
+          <t>1.99%441,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2.05%</t>
+          <t>1.99%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>477100</v>
+        <v>441000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-14 19:16:58</t>
+          <t>2026-09-14 23:57:54</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -839,12 +839,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.98%716,000</t>
+          <t>1.94%716,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1.98%</t>
+          <t>1.94%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-14 19:16:58</t>
+          <t>2026-09-14 23:57:54</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -902,12 +902,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.97%16,304</t>
+          <t>1.93%16,304</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>1.97%</t>
+          <t>1.93%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-14 19:16:58</t>
+          <t>2026-09-14 23:57:54</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-14 19:16:58</t>
+          <t>2026-09-14 23:57:54</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.71%88,100</t>
+          <t>1.59%88,100</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>1.71%</t>
+          <t>1.59%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-14 19:16:58</t>
+          <t>2026-09-14 23:57:54</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1071,40 +1071,40 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>4062IBIDEN CO LTD</t>
+          <t>3017奇鋐</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-1.78%3310</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-1.78%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3310</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.55%130,900</t>
+          <t>1.48%158,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1.55%</t>
+          <t>1.48%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>130900</v>
+        <v>158000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-14 19:16:58</t>
+          <t>2026-09-14 23:57:54</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1134,40 +1134,40 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3017奇鋐</t>
+          <t>4062IBIDEN CO LTD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-1.78%3310</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-1.78%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3310</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.52%158,000</t>
+          <t>1.46%130,900</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>1.46%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>158000</v>
+        <v>130900</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-14 19:16:59</t>
+          <t>2026-09-14 23:57:55</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1.40%90,000</t>
+          <t>1.41%90,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1.40%</t>
+          <t>1.41%</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-14 19:16:59</t>
+          <t>2026-09-14 23:57:55</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1280,12 +1280,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1.26%1,665,000</t>
+          <t>1.22%1,665,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>1.26%</t>
+          <t>1.22%</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-14 19:16:59</t>
+          <t>2026-09-14 23:57:55</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1323,40 +1323,40 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2345智邦</t>
+          <t>8046南電</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-0.53%1875</t>
+          <t>-2.31%1055</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-0.53%</t>
+          <t>-2.31%</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1875</t>
+          <t>1055</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.94%172,000</t>
+          <t>0.91%302,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.91%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>172000</v>
+        <v>302000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-14 19:16:59</t>
+          <t>2026-09-14 23:57:55</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1386,40 +1386,40 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>6274台燿</t>
+          <t>2360致茂</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-2.15%1365</t>
+          <t>-0.93%2140</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-2.15%</t>
+          <t>-0.93%</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1365</t>
+          <t>2140</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.91%236,000</t>
+          <t>0.78%130,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>0.78%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>236000</v>
+        <v>130000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-14 19:16:59</t>
+          <t>2026-09-14 23:57:55</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1449,40 +1449,40 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>8046南電</t>
+          <t>3529力旺</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-2.31%1055</t>
+          <t>-5.49%2580</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-2.31%</t>
+          <t>-5.49%</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1055</t>
+          <t>2580</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.90%302,000</t>
+          <t>0.76%106,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.90%</t>
+          <t>0.76%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>302000</v>
+        <v>106000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-14 19:16:59</t>
+          <t>2026-09-14 23:57:55</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1512,40 +1512,40 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3529力旺</t>
+          <t>7769鴻勁</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-5.49%2580</t>
+          <t>-0.08%6305</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-5.49%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2580</t>
+          <t>6305</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.80%106,000</t>
+          <t>0.72%41,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0.80%</t>
+          <t>0.72%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>106000</v>
+        <v>41000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-14 19:16:59</t>
+          <t>2026-09-14 23:57:55</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1575,169 +1575,43 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2360致茂</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-0.93%2140</t>
+          <t>+4.27%1955</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-0.93%</t>
+          <t>+4.27%</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2140</t>
+          <t>1955</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.79%130,000</t>
+          <t>0.49%94,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.79%</t>
+          <t>0.49%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>130000</v>
+        <v>94000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>00990A</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2026-09-14 19:16:59</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>3</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>7769鴻勁</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>-0.08%6305</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>-0.08%</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>6305</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>0.74%41,000</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>0.74%</t>
-        </is>
-      </c>
-      <c r="K20" t="n">
-        <v>41000</v>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>-0.00%</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>00990A</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2026-09-14 19:17:01</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>4</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>3665貿聯-KY</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>+4.27%1955</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>+4.27%</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>1955</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>0.50%94,000</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>0.50%</t>
-        </is>
-      </c>
-      <c r="K21" t="n">
-        <v>94000</v>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>+0.02%</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
         <is>
           <t>登入查看</t>
         </is>
